--- a/Result/profitability/6241.xlsx
+++ b/Result/profitability/6241.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1375</v>
+        <v>-0.09624999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>16.59375</v>
+        <v>16.97375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.13125</v>
+        <v>-0.07624999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>14.71375</v>
+        <v>14.87625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03374999999999999</v>
+        <v>-0.07124999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>17.70125</v>
+        <v>17.12375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09374999999999997</v>
+        <v>-0.06624999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>16.59</v>
+        <v>16.56125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04624999999999999</v>
+        <v>-0.08249999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>18.1525</v>
+        <v>18.40125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01499999999999998</v>
+        <v>-0.07374999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>21.525</v>
+        <v>21.465</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04125000000000002</v>
+        <v>-0.04749999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>24.42125</v>
+        <v>24</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6241</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>187</v>
+      </c>
+      <c r="D75" t="n">
+        <v>159</v>
+      </c>
+      <c r="E75" t="n">
+        <v>28</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.32625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.543478260869565</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.369999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1831521739130435</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4680851063829787</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.2300000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01507208387942338</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
